--- a/B_Inputs/AC_seed/T12_policy_settings.xlsx
+++ b/B_Inputs/AC_seed/T12_policy_settings.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2071,6 +2071,60 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>Reject ZIP members compressed more than this ratio (zip-bomb guard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>production_phases</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Monitoring; Reg/Audit</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Lifecycle phases counted as 'in production' on the Command Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>insights_display_limit</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Number of governance insights shown on the Command Center (all are available on request)</t>
         </is>
       </c>
     </row>

--- a/B_Inputs/AC_seed/T12_policy_settings.xlsx
+++ b/B_Inputs/AC_seed/T12_policy_settings.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1294,39 +1294,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>model_types</t>
+          <t>monitoring_phase</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Credit Risk; Provisioning; Balance Sheet; Forecasting; CCAR/Stress Testing</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Lifecycle</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Allowed model types</t>
+          <t>Lifecycle phase the derived Revalidation column is taken from (R3); must be one of lifecycle_phases</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>validation_types</t>
+          <t>model_types</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Initial; Periodic; Targeted; Change</t>
+          <t>Credit Risk; Provisioning; Balance Sheet; Forecasting; CCAR/Stress Testing</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Allowed validation types (BRD §9)</t>
+          <t>Allowed model types</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>validation_outcomes</t>
+          <t>validation_types</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Approved; Conditional; Rejected; In Progress</t>
+          <t>Initial; Periodic; Targeted; Change</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1368,19 +1368,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Allowed validation outcomes (BRD §9)</t>
+          <t>Allowed validation types (BRD §9)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>validation_currency_outcomes</t>
+          <t>validation_outcomes</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Approved; Conditional</t>
+          <t>Approved; Conditional; Rejected; In Progress</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1395,19 +1395,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Completed outcomes that reset the last validation date</t>
+          <t>Allowed validation outcomes (BRD §9)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>finding_severities</t>
+          <t>validation_currency_outcomes</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Critical; Medium; Low</t>
+          <t>Approved; Conditional</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1417,24 +1417,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Findings</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Finding severities (BRD §11)</t>
+          <t>Completed outcomes that reset the last validation date</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>finding_categories</t>
+          <t>finding_severities</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Data; Methodology; Documentation; Implementation; Performance; Monitoring</t>
+          <t>Critical; Medium; Low</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1449,19 +1449,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Finding categories</t>
+          <t>Finding severities (BRD §11)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>finding_statuses</t>
+          <t>finding_categories</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Open; In Progress; Deferred; Closed; Accepted Risk; Rejected</t>
+          <t>Data; Methodology; Documentation; Implementation; Performance; Monitoring</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Finding statuses (BRD §11)</t>
+          <t>Finding categories</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>finding_open_statuses</t>
+          <t>finding_statuses</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Open; In Progress; Deferred</t>
+          <t>Open; In Progress; Deferred; Closed; Accepted Risk; Rejected</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1503,19 +1503,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Statuses counted as open for remediation and ageing</t>
+          <t>Finding statuses (BRD §11)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>finding_sources</t>
+          <t>finding_open_statuses</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Manual; Import; Extraction; Monitoring</t>
+          <t>Open; In Progress; Deferred</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1530,19 +1530,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finding sources</t>
+          <t>Statuses counted as open for remediation and ageing</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>approval_forums</t>
+          <t>finding_sources</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MRC; Model Risk Officer; Validation Committee</t>
+          <t>Manual; Import; Extraction; Monitoring</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1552,24 +1552,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Approval forums</t>
+          <t>Finding sources</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>approval_decision_types</t>
+          <t>approval_forums</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ToR; Initial approval; Validation complete; Pre-implementation; Annual review; Periodic review; Model change; Retirement</t>
+          <t>MRC; Model Risk Officer; Validation Committee</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Approval decision types</t>
+          <t>Approval forums</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>approval_decisions</t>
+          <t>approval_decision_types</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Approved; Conditional; Rejected</t>
+          <t>ToR; Initial approval; Validation complete; Pre-implementation; Annual review; Periodic review; Model change; Retirement</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1611,46 +1611,46 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Approval decisions (BRD §12)</t>
+          <t>Approval decision types</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>score_validation_overdue_penalty_per_day</t>
+          <t>approval_decisions</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Approved; Conditional; Rejected</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Governance score</t>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Validation currency points lost per day overdue (R8)</t>
+          <t>Approval decisions (BRD §12)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>score_penalty_open_critical</t>
+          <t>score_validation_overdue_penalty_per_day</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1665,19 +1665,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per open Critical finding (R8)</t>
+          <t>Validation currency points lost per day overdue (R8)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>score_penalty_open_medium</t>
+          <t>score_penalty_open_critical</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1692,19 +1692,19 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per open Medium finding (R8)</t>
+          <t>Issue remediation points lost per open Critical finding (R8)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>score_penalty_open_low</t>
+          <t>score_penalty_open_medium</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1719,19 +1719,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per open Low finding (R8)</t>
+          <t>Issue remediation points lost per open Medium finding (R8)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>score_penalty_past_due</t>
+          <t>score_penalty_open_low</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1746,19 +1746,19 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per finding past due (R8)</t>
+          <t>Issue remediation points lost per open Low finding (R8)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>score_mrc_conditional</t>
+          <t>score_penalty_past_due</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1773,46 +1773,46 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MRC compliance score for a Conditional decision with open conditions (R8)</t>
+          <t>Issue remediation points lost per finding past due (R8)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>import_max_file_mb</t>
+          <t>score_mrc_conditional</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Governance score</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Maximum size of one structured import file (Excel/CSV)</t>
+          <t>MRC compliance score for a Conditional decision with open conditions (R8)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>import_max_files</t>
+          <t>import_max_file_mb</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1827,19 +1827,19 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Maximum number of files in one import batch</t>
+          <t>Maximum size of one structured import file (Excel/CSV)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>import_max_rows</t>
+          <t>import_max_files</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1854,46 +1854,46 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Maximum data rows in one import file</t>
+          <t>Maximum number of files in one import batch</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>document_type_keywords</t>
+          <t>import_max_rows</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Terms of Reference=terms of reference|tor; Model Development Document=model development|mdd|development document; Validation Report=validation report|validation|vr; Monitoring Plan=monitoring plan|mon plan; Backtesting Report=backtesting|backtest; Monitoring Report=monitoring report|monitoring|kpi; Model Approval/MRC Paper=mrc|approval|committee paper; Model Change Document=model change|change request; Data Quality Report=data quality|dq report|dq; Regulatory/Audit Evidence=regulatory|audit|supervisory; Model Inventory Evidence=inventory</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Classification keywords per document type, checked in this order against file then folder names (BRD §34)</t>
+          <t>Maximum data rows in one import file</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>allowed_document_extensions</t>
+          <t>document_type_keywords</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>pdf; docx; xlsx; pptx; csv</t>
+          <t>Terms of Reference=terms of reference|tor; Model Development Document=model development|mdd|development document; Validation Report=validation report|validation|vr; Monitoring Plan=monitoring plan|mon plan; Backtesting Report=backtesting|backtest; Monitoring Report=monitoring report|monitoring|kpi; Model Approval/MRC Paper=mrc|approval|committee paper; Model Change Document=model change|change request; Data Quality Report=data quality|dq report|dq; Regulatory/Audit Evidence=regulatory|audit|supervisory; Model Inventory Evidence=inventory</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1903,24 +1903,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>File types accepted as documents or evidence</t>
+          <t>Classification keywords per document type, checked in this order against file then folder names (BRD §34)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>document_confidentiality_levels</t>
+          <t>allowed_document_extensions</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Internal; Confidential; Restricted</t>
+          <t>pdf; docx; xlsx; pptx; csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1930,29 +1930,29 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Confidentiality classifications</t>
+          <t>File types accepted as documents or evidence</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>document_default_confidentiality</t>
+          <t>document_confidentiality_levels</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Internal; Confidential; Restricted</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1962,24 +1962,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Confidentiality applied when none is given</t>
+          <t>Confidentiality classifications</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>document_retention_years</t>
+          <t>document_default_confidentiality</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1989,24 +1989,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Retention period from the effective date (BRD §68)</t>
+          <t>Confidentiality applied when none is given</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>document_auto_confirm_confidence</t>
+          <t>document_retention_years</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2016,46 +2016,46 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Minimum classification confidence for a system (seed) load to store without review</t>
+          <t>Retention period from the effective date (BRD §68)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>max_zip_uncompressed_mb</t>
+          <t>document_auto_confirm_confidence</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Maximum total size of files inside a ZIP package</t>
+          <t>Minimum classification confidence for a system (seed) load to store without review</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>max_zip_compression_ratio</t>
+          <t>max_zip_uncompressed_mb</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2070,59 +2070,86 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Reject ZIP members compressed more than this ratio (zip-bomb guard)</t>
+          <t>Maximum total size of files inside a ZIP package</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>production_phases</t>
+          <t>max_zip_compression_ratio</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Monitoring; Reg/Audit</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lifecycle phases counted as 'in production' on the Command Center</t>
+          <t>Reject ZIP members compressed more than this ratio (zip-bomb guard)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>production_phases</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Monitoring; Reg/Audit</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Lifecycle phases counted as 'in production' on the Command Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>insights_display_limit</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Number of governance insights shown on the Command Center (all are available on request)</t>
         </is>

--- a/B_Inputs/AC_seed/T12_policy_settings.xlsx
+++ b/B_Inputs/AC_seed/T12_policy_settings.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,66 +1321,66 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>model_types</t>
+          <t>score_band_warn_min</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Credit Risk; Provisioning; Balance Sheet; Forecasting; CCAR/Stress Testing</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Allowed model types</t>
+          <t>Governance score at or above which a model is amber rather than red (R8 bands)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>validation_types</t>
+          <t>score_band_good_min</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Initial; Periodic; Targeted; Change</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Allowed validation types (BRD §9)</t>
+          <t>Governance score at or above which a model is green (R8 bands)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>validation_outcomes</t>
+          <t>model_types</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Approved; Conditional; Rejected; In Progress</t>
+          <t>Credit Risk; Provisioning; Balance Sheet; Forecasting; CCAR/Stress Testing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1390,24 +1390,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Allowed validation outcomes (BRD §9)</t>
+          <t>Allowed model types</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>validation_currency_outcomes</t>
+          <t>validation_types</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Approved; Conditional</t>
+          <t>Initial; Periodic; Targeted; Change</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1422,19 +1422,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Completed outcomes that reset the last validation date</t>
+          <t>Allowed validation types (BRD §9)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>finding_severities</t>
+          <t>validation_outcomes</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Critical; Medium; Low</t>
+          <t>Approved; Conditional; Rejected; In Progress</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1444,24 +1444,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Findings</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Finding severities (BRD §11)</t>
+          <t>Allowed validation outcomes (BRD §9)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>finding_categories</t>
+          <t>validation_currency_outcomes</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Data; Methodology; Documentation; Implementation; Performance; Monitoring</t>
+          <t>Approved; Conditional</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1471,24 +1471,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Findings</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Finding categories</t>
+          <t>Completed outcomes that reset the last validation date</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>finding_statuses</t>
+          <t>finding_severities</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Open; In Progress; Deferred; Closed; Accepted Risk; Rejected</t>
+          <t>Critical; Medium; Low</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1503,19 +1503,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Finding statuses (BRD §11)</t>
+          <t>Finding severities (BRD §11)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>finding_open_statuses</t>
+          <t>finding_categories</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Open; In Progress; Deferred</t>
+          <t>Data; Methodology; Documentation; Implementation; Performance; Monitoring</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1530,19 +1530,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Statuses counted as open for remediation and ageing</t>
+          <t>Finding categories</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>finding_sources</t>
+          <t>finding_statuses</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Manual; Import; Extraction; Monitoring</t>
+          <t>Open; In Progress; Deferred; Closed; Accepted Risk; Rejected</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1557,19 +1557,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Finding sources</t>
+          <t>Finding statuses (BRD §11)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>approval_forums</t>
+          <t>finding_open_statuses</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MRC; Model Risk Officer; Validation Committee</t>
+          <t>Open; In Progress; Deferred</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1579,24 +1579,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Approval forums</t>
+          <t>Statuses counted as open for remediation and ageing</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>approval_decision_types</t>
+          <t>finding_sources</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ToR; Initial approval; Validation complete; Pre-implementation; Annual review; Periodic review; Model change; Retirement</t>
+          <t>Manual; Import; Extraction; Monitoring</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1606,24 +1606,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Approval decision types</t>
+          <t>Finding sources</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>approval_decisions</t>
+          <t>approval_forums</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Approved; Conditional; Rejected</t>
+          <t>MRC; Model Risk Officer; Validation Committee</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1638,73 +1638,73 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Approval decisions (BRD §12)</t>
+          <t>Approval forums</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>score_validation_overdue_penalty_per_day</t>
+          <t>approval_decision_types</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>ToR; Initial approval; Validation complete; Pre-implementation; Annual review; Periodic review; Model change; Retirement</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Governance score</t>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Validation currency points lost per day overdue (R8)</t>
+          <t>Approval decision types</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>score_penalty_open_critical</t>
+          <t>approval_decisions</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Approved; Conditional; Rejected</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Governance score</t>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per open Critical finding (R8)</t>
+          <t>Approval decisions (BRD §12)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>score_penalty_open_medium</t>
+          <t>score_validation_overdue_penalty_per_day</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1719,19 +1719,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per open Medium finding (R8)</t>
+          <t>Validation currency points lost per day overdue (R8)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>score_penalty_open_low</t>
+          <t>score_penalty_open_critical</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1746,14 +1746,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per open Low finding (R8)</t>
+          <t>Issue remediation points lost per open Critical finding (R8)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>score_penalty_past_due</t>
+          <t>score_penalty_open_medium</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1773,19 +1773,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per finding past due (R8)</t>
+          <t>Issue remediation points lost per open Medium finding (R8)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>score_mrc_conditional</t>
+          <t>score_penalty_open_low</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1800,73 +1800,73 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MRC compliance score for a Conditional decision with open conditions (R8)</t>
+          <t>Issue remediation points lost per open Low finding (R8)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>import_max_file_mb</t>
+          <t>score_penalty_past_due</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Governance score</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Maximum size of one structured import file (Excel/CSV)</t>
+          <t>Issue remediation points lost per finding past due (R8)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>import_max_files</t>
+          <t>score_mrc_conditional</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Governance score</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Maximum number of files in one import batch</t>
+          <t>MRC compliance score for a Conditional decision with open conditions (R8)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>import_max_rows</t>
+          <t>import_max_file_mb</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1881,51 +1881,51 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Maximum data rows in one import file</t>
+          <t>Maximum size of one structured import file (Excel/CSV)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>document_type_keywords</t>
+          <t>import_max_files</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Terms of Reference=terms of reference|tor; Model Development Document=model development|mdd|development document; Validation Report=validation report|validation|vr; Monitoring Plan=monitoring plan|mon plan; Backtesting Report=backtesting|backtest; Monitoring Report=monitoring report|monitoring|kpi; Model Approval/MRC Paper=mrc|approval|committee paper; Model Change Document=model change|change request; Data Quality Report=data quality|dq report|dq; Regulatory/Audit Evidence=regulatory|audit|supervisory; Model Inventory Evidence=inventory</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Classification keywords per document type, checked in this order against file then folder names (BRD §34)</t>
+          <t>Maximum number of files in one import batch</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>allowed_document_extensions</t>
+          <t>import_max_rows</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>pdf; docx; xlsx; pptx; csv</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1935,19 +1935,19 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>File types accepted as documents or evidence</t>
+          <t>Maximum data rows in one import file</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>document_confidentiality_levels</t>
+          <t>document_type_keywords</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Internal; Confidential; Restricted</t>
+          <t>Terms of Reference=terms of reference|tor; Model Development Document=model development|mdd|development document; Validation Report=validation report|validation|vr; Monitoring Plan=monitoring plan|mon plan; Backtesting Report=backtesting|backtest; Monitoring Report=monitoring report|monitoring|kpi; Model Approval/MRC Paper=mrc|approval|committee paper; Model Change Document=model change|change request; Data Quality Report=data quality|dq report|dq; Regulatory/Audit Evidence=regulatory|audit|supervisory; Model Inventory Evidence=inventory</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1962,51 +1962,51 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Confidentiality classifications</t>
+          <t>Classification keywords per document type, checked in this order against file then folder names (BRD §34)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>document_default_confidentiality</t>
+          <t>allowed_document_extensions</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>pdf; docx; xlsx; pptx; csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Confidentiality applied when none is given</t>
+          <t>File types accepted as documents or evidence</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>document_retention_years</t>
+          <t>document_confidentiality_levels</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Internal; Confidential; Restricted</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2016,24 +2016,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Retention period from the effective date (BRD §68)</t>
+          <t>Confidentiality classifications</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>document_auto_confirm_confidence</t>
+          <t>document_default_confidentiality</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2043,19 +2043,19 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Minimum classification confidence for a system (seed) load to store without review</t>
+          <t>Confidentiality applied when none is given</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>max_zip_uncompressed_mb</t>
+          <t>document_retention_years</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2065,91 +2065,145 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Maximum total size of files inside a ZIP package</t>
+          <t>Retention period from the effective date (BRD §68)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>max_zip_compression_ratio</t>
+          <t>document_auto_confirm_confidence</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Reject ZIP members compressed more than this ratio (zip-bomb guard)</t>
+          <t>Minimum classification confidence for a system (seed) load to store without review</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>production_phases</t>
+          <t>max_zip_uncompressed_mb</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Monitoring; Reg/Audit</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lifecycle phases counted as 'in production' on the Command Center</t>
+          <t>Maximum total size of files inside a ZIP package</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>max_zip_compression_ratio</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Reject ZIP members compressed more than this ratio (zip-bomb guard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>production_phases</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Monitoring; Reg/Audit</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Lifecycle phases counted as 'in production' on the Command Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>insights_display_limit</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Number of governance insights shown on the Command Center (all are available on request)</t>
         </is>

--- a/B_Inputs/AC_seed/T12_policy_settings.xlsx
+++ b/B_Inputs/AC_seed/T12_policy_settings.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1105,12 +1105,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>max_document_size_mb</t>
+          <t>warning_escalation_periods</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1120,51 +1120,51 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maximum size of an individual uploaded document</t>
+          <t>Consecutive warning periods before a metric escalates (BRD §21)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>max_zip_size_mb</t>
+          <t>breach_severity_rules</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>metric_warn=Low; metric_fail=Medium; data_quality_fail=High; regulatory_metric_fail=High; repeated_breach=High; high_tier_critical_metric_fail=Critical</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maximum size of an uploaded ZIP package</t>
+          <t>Breach severity rules as Condition=Severity (BRD §21, §81A D5); first match from the most specific wins</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>max_zip_file_count</t>
+          <t>max_document_size_mb</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1179,78 +1179,78 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Maximum number of files in a ZIP package</t>
+          <t>Maximum size of an individual uploaded document</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>lifecycle_phases</t>
+          <t>max_zip_size_mb</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Initiation; Development; Validation; Implementation; Monitoring; Reg/Audit; Retirement</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lifecycle</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lifecycle phases in order (BRD §8)</t>
+          <t>Maximum size of an uploaded ZIP package</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mrc_required_from_phase</t>
+          <t>max_zip_file_count</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lifecycle</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Phase from which an MRC decision is required (R8 MRC compliance)</t>
+          <t>Maximum number of files in a ZIP package</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>validator_required_from_phase</t>
+          <t>lifecycle_phases</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Initiation; Development; Validation; Implementation; Monitoring; Reg/Audit; Retirement</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1260,19 +1260,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Phase from which a validator must be assigned</t>
+          <t>Lifecycle phases in order (BRD §8)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>validation_data_required_from_phase</t>
+          <t>mrc_required_from_phase</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1287,19 +1287,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Phase from which go-live date, revalidation frequency and last validation date are required</t>
+          <t>Phase from which an MRC decision is required (R8 MRC compliance)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>monitoring_phase</t>
+          <t>validator_required_from_phase</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1314,127 +1314,127 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lifecycle phase the derived Revalidation column is taken from (R3); must be one of lifecycle_phases</t>
+          <t>Phase from which a validator must be assigned</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>score_band_warn_min</t>
+          <t>validation_data_required_from_phase</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Lifecycle</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Governance score at or above which a model is amber rather than red (R8 bands)</t>
+          <t>Phase from which go-live date, revalidation frequency and last validation date are required</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>score_band_good_min</t>
+          <t>monitoring_phase</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Lifecycle</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Governance score at or above which a model is green (R8 bands)</t>
+          <t>Lifecycle phase the derived Revalidation column is taken from (R3); must be one of lifecycle_phases</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>model_types</t>
+          <t>score_band_warn_min</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Credit Risk; Provisioning; Balance Sheet; Forecasting; CCAR/Stress Testing</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Allowed model types</t>
+          <t>Governance score at or above which a model is amber rather than red (R8 bands)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>validation_types</t>
+          <t>score_band_good_min</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Initial; Periodic; Targeted; Change</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Allowed validation types (BRD §9)</t>
+          <t>Governance score at or above which a model is green (R8 bands)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>validation_outcomes</t>
+          <t>model_types</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Approved; Conditional; Rejected; In Progress</t>
+          <t>Credit Risk; Provisioning; Balance Sheet; Forecasting; CCAR/Stress Testing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1444,24 +1444,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Allowed validation outcomes (BRD §9)</t>
+          <t>Allowed model types</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>validation_currency_outcomes</t>
+          <t>validation_types</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Approved; Conditional</t>
+          <t>Initial; Periodic; Targeted; Change</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Completed outcomes that reset the last validation date</t>
+          <t>Allowed validation types (BRD §9)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>finding_severities</t>
+          <t>validation_outcomes</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Critical; Medium; Low</t>
+          <t>Approved; Conditional; Rejected; In Progress</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1498,24 +1498,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Findings</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Finding severities (BRD §11)</t>
+          <t>Allowed validation outcomes (BRD §9)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>finding_categories</t>
+          <t>validation_currency_outcomes</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Data; Methodology; Documentation; Implementation; Performance; Monitoring</t>
+          <t>Approved; Conditional</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1525,24 +1525,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Findings</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finding categories</t>
+          <t>Completed outcomes that reset the last validation date</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>finding_statuses</t>
+          <t>finding_severities</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Open; In Progress; Deferred; Closed; Accepted Risk; Rejected</t>
+          <t>Critical; Medium; Low</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1557,19 +1557,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Finding statuses (BRD §11)</t>
+          <t>Finding severities (BRD §11)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>finding_open_statuses</t>
+          <t>finding_categories</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Open; In Progress; Deferred</t>
+          <t>Data; Methodology; Documentation; Implementation; Performance; Monitoring</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Statuses counted as open for remediation and ageing</t>
+          <t>Finding categories</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>finding_sources</t>
+          <t>finding_statuses</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Manual; Import; Extraction; Monitoring</t>
+          <t>Open; In Progress; Deferred; Closed; Accepted Risk; Rejected</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1611,19 +1611,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Finding sources</t>
+          <t>Finding statuses (BRD §11)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>approval_forums</t>
+          <t>finding_open_statuses</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MRC; Model Risk Officer; Validation Committee</t>
+          <t>Open; In Progress; Deferred</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1633,24 +1633,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Approval forums</t>
+          <t>Statuses counted as open for remediation and ageing</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>approval_decision_types</t>
+          <t>finding_sources</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ToR; Initial approval; Validation complete; Pre-implementation; Annual review; Periodic review; Model change; Retirement</t>
+          <t>Manual; Import; Extraction; Monitoring</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1660,24 +1660,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Approval decision types</t>
+          <t>Finding sources</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>approval_decisions</t>
+          <t>approval_forums</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Approved; Conditional; Rejected</t>
+          <t>MRC; Model Risk Officer; Validation Committee</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1692,73 +1692,73 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Approval decisions (BRD §12)</t>
+          <t>Approval forums</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>score_validation_overdue_penalty_per_day</t>
+          <t>approval_decision_types</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>ToR; Initial approval; Validation complete; Pre-implementation; Annual review; Periodic review; Model change; Retirement</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Governance score</t>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Validation currency points lost per day overdue (R8)</t>
+          <t>Approval decision types</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>score_penalty_open_critical</t>
+          <t>approval_decisions</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Approved; Conditional; Rejected</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Governance score</t>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per open Critical finding (R8)</t>
+          <t>Approval decisions (BRD §12)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>score_penalty_open_medium</t>
+          <t>score_validation_overdue_penalty_per_day</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1773,19 +1773,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per open Medium finding (R8)</t>
+          <t>Validation currency points lost per day overdue (R8)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>score_penalty_open_low</t>
+          <t>score_penalty_open_critical</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1800,14 +1800,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per open Low finding (R8)</t>
+          <t>Issue remediation points lost per open Critical finding (R8)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>score_penalty_past_due</t>
+          <t>score_penalty_open_medium</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1827,19 +1827,19 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per finding past due (R8)</t>
+          <t>Issue remediation points lost per open Medium finding (R8)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>score_mrc_conditional</t>
+          <t>score_penalty_open_low</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1854,73 +1854,73 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MRC compliance score for a Conditional decision with open conditions (R8)</t>
+          <t>Issue remediation points lost per open Low finding (R8)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>import_max_file_mb</t>
+          <t>score_penalty_past_due</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Governance score</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Maximum size of one structured import file (Excel/CSV)</t>
+          <t>Issue remediation points lost per finding past due (R8)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>import_max_files</t>
+          <t>score_mrc_conditional</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Governance score</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Maximum number of files in one import batch</t>
+          <t>MRC compliance score for a Conditional decision with open conditions (R8)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>import_max_rows</t>
+          <t>import_max_file_mb</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1935,51 +1935,51 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Maximum data rows in one import file</t>
+          <t>Maximum size of one structured import file (Excel/CSV)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>document_type_keywords</t>
+          <t>import_max_files</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Terms of Reference=terms of reference|tor; Model Development Document=model development|mdd|development document; Validation Report=validation report|validation|vr; Monitoring Plan=monitoring plan|mon plan; Backtesting Report=backtesting|backtest; Monitoring Report=monitoring report|monitoring|kpi; Model Approval/MRC Paper=mrc|approval|committee paper; Model Change Document=model change|change request; Data Quality Report=data quality|dq report|dq; Regulatory/Audit Evidence=regulatory|audit|supervisory; Model Inventory Evidence=inventory</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Classification keywords per document type, checked in this order against file then folder names (BRD §34)</t>
+          <t>Maximum number of files in one import batch</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>allowed_document_extensions</t>
+          <t>import_max_rows</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>pdf; docx; xlsx; pptx; csv</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1989,19 +1989,19 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>File types accepted as documents or evidence</t>
+          <t>Maximum data rows in one import file</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>document_confidentiality_levels</t>
+          <t>document_type_keywords</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Internal; Confidential; Restricted</t>
+          <t>Terms of Reference=terms of reference|tor; Model Development Document=model development|mdd|development document; Validation Report=validation report|validation|vr; Monitoring Plan=monitoring plan|mon plan; Backtesting Report=backtesting|backtest; Monitoring Report=monitoring report|monitoring|kpi; Model Approval/MRC Paper=mrc|approval|committee paper; Model Change Document=model change|change request; Data Quality Report=data quality|dq report|dq; Regulatory/Audit Evidence=regulatory|audit|supervisory; Model Inventory Evidence=inventory</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2016,51 +2016,51 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Confidentiality classifications</t>
+          <t>Classification keywords per document type, checked in this order against file then folder names (BRD §34)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>document_default_confidentiality</t>
+          <t>allowed_document_extensions</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>pdf; docx; xlsx; pptx; csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Confidentiality applied when none is given</t>
+          <t>File types accepted as documents or evidence</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>document_retention_years</t>
+          <t>document_confidentiality_levels</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Internal; Confidential; Restricted</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2070,24 +2070,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Retention period from the effective date (BRD §68)</t>
+          <t>Confidentiality classifications</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>document_auto_confirm_confidence</t>
+          <t>document_default_confidentiality</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2097,19 +2097,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Minimum classification confidence for a system (seed) load to store without review</t>
+          <t>Confidentiality applied when none is given</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>max_zip_uncompressed_mb</t>
+          <t>document_retention_years</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2119,91 +2119,145 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Maximum total size of files inside a ZIP package</t>
+          <t>Retention period from the effective date (BRD §68)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>max_zip_compression_ratio</t>
+          <t>document_auto_confirm_confidence</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Reject ZIP members compressed more than this ratio (zip-bomb guard)</t>
+          <t>Minimum classification confidence for a system (seed) load to store without review</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>production_phases</t>
+          <t>max_zip_uncompressed_mb</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Monitoring; Reg/Audit</t>
+          <t>500</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lifecycle phases counted as 'in production' on the Command Center</t>
+          <t>Maximum total size of files inside a ZIP package</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>max_zip_compression_ratio</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Reject ZIP members compressed more than this ratio (zip-bomb guard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>production_phases</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Monitoring; Reg/Audit</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Lifecycle phases counted as 'in production' on the Command Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>insights_display_limit</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Number of governance insights shown on the Command Center (all are available on request)</t>
         </is>

--- a/B_Inputs/AC_seed/T12_policy_settings.xlsx
+++ b/B_Inputs/AC_seed/T12_policy_settings.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2260,6 +2260,33 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>Number of governance insights shown on the Command Center (all are available on request)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>regulatory_framework</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SR 26-2 / OCC Bulletin 2026-13</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Governance score</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Framework label shown on the model risk report header (REQ-REG-10A)</t>
         </is>
       </c>
     </row>

--- a/B_Inputs/AC_seed/T12_policy_settings.xlsx
+++ b/B_Inputs/AC_seed/T12_policy_settings.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2287,6 +2287,33 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>Framework label shown on the model risk report header (REQ-REG-10A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>report_lowest_scoring_limit</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Number of lowest-scoring models listed in the model risk report (REQ-REG-10A)</t>
         </is>
       </c>
     </row>

--- a/B_Inputs/AC_seed/T12_policy_settings.xlsx
+++ b/B_Inputs/AC_seed/T12_policy_settings.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Required document types from Implementation onwards (BRD §40)</t>
+          <t>Required document types from required_docs_production_from_phase onwards (BRD §40)</t>
         </is>
       </c>
     </row>
@@ -1375,147 +1375,147 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>score_band_warn_min</t>
+          <t>required_docs_development_from_phase</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Governance score at or above which a model is amber rather than red (R8 bands)</t>
+          <t>Phase from which required_docs_development applies (BRD §40); must be one of lifecycle_phases</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>score_band_good_min</t>
+          <t>required_docs_validation_from_phase</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Governance score at or above which a model is green (R8 bands)</t>
+          <t>Phase from which required_docs_validation applies (BRD §40); must be one of lifecycle_phases</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>model_types</t>
+          <t>required_docs_production_from_phase</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Credit Risk; Provisioning; Balance Sheet; Forecasting; CCAR/Stress Testing</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Allowed model types</t>
+          <t>Phase from which required_docs_production applies (BRD §40); must be one of lifecycle_phases</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>validation_types</t>
+          <t>score_band_warn_min</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Initial; Periodic; Targeted; Change</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Allowed validation types (BRD §9)</t>
+          <t>Governance score at or above which a model is amber rather than red (R8 bands)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>validation_outcomes</t>
+          <t>score_band_good_min</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Approved; Conditional; Rejected; In Progress</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Allowed validation outcomes (BRD §9)</t>
+          <t>Governance score at or above which a model is green (R8 bands)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>validation_currency_outcomes</t>
+          <t>model_types</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Approved; Conditional</t>
+          <t>Credit Risk; Provisioning; Balance Sheet; Forecasting; CCAR/Stress Testing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1525,24 +1525,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Completed outcomes that reset the last validation date</t>
+          <t>Allowed model types</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>finding_severities</t>
+          <t>validation_types</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Critical; Medium; Low</t>
+          <t>Initial; Periodic; Targeted; Change</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1552,24 +1552,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Findings</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Finding severities (BRD §11)</t>
+          <t>Allowed validation types (BRD §9)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>finding_categories</t>
+          <t>validation_outcomes</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Data; Methodology; Documentation; Implementation; Performance; Monitoring</t>
+          <t>Approved; Conditional; Rejected; In Progress</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1579,24 +1579,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Findings</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Finding categories</t>
+          <t>Allowed validation outcomes (BRD §9)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>finding_statuses</t>
+          <t>validation_currency_outcomes</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Open; In Progress; Deferred; Closed; Accepted Risk; Rejected</t>
+          <t>Approved; Conditional</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1606,24 +1606,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Findings</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Finding statuses (BRD §11)</t>
+          <t>Completed outcomes that reset the last validation date</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>finding_open_statuses</t>
+          <t>finding_severities</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Open; In Progress; Deferred</t>
+          <t>Critical; Medium; Low</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1638,19 +1638,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Statuses counted as open for remediation and ageing</t>
+          <t>Finding severities (BRD §11)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>finding_sources</t>
+          <t>finding_categories</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Manual; Import; Extraction; Monitoring</t>
+          <t>Data; Methodology; Documentation; Implementation; Performance; Monitoring</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1665,19 +1665,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Finding sources</t>
+          <t>Finding categories</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>approval_forums</t>
+          <t>finding_statuses</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MRC; Model Risk Officer; Validation Committee</t>
+          <t>Open; In Progress; Deferred; Closed; Accepted Risk; Rejected</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1687,24 +1687,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Approval forums</t>
+          <t>Finding statuses (BRD §11)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>approval_decision_types</t>
+          <t>finding_open_statuses</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ToR; Initial approval; Validation complete; Pre-implementation; Annual review; Periodic review; Model change; Retirement</t>
+          <t>Open; In Progress; Deferred</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1714,24 +1714,24 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Approval decision types</t>
+          <t>Statuses counted as open for remediation and ageing</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>approval_decisions</t>
+          <t>finding_sources</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Approved; Conditional; Rejected</t>
+          <t>Manual; Import; Extraction; Monitoring</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1741,105 +1741,105 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Approval decisions (BRD §12)</t>
+          <t>Finding sources</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>score_validation_overdue_penalty_per_day</t>
+          <t>approval_forums</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>MRC; Model Risk Officer; Validation Committee</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Governance score</t>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Validation currency points lost per day overdue (R8)</t>
+          <t>Approval forums</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>score_penalty_open_critical</t>
+          <t>approval_decision_types</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>ToR; Initial approval; Validation complete; Pre-implementation; Annual review; Periodic review; Model change; Retirement</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Governance score</t>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per open Critical finding (R8)</t>
+          <t>Approval decision types</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>score_penalty_open_medium</t>
+          <t>approval_decisions</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Approved; Conditional; Rejected</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Governance score</t>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per open Medium finding (R8)</t>
+          <t>Approval decisions (BRD §12)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>score_penalty_open_low</t>
+          <t>score_validation_overdue_penalty_per_day</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1854,19 +1854,19 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per open Low finding (R8)</t>
+          <t>Validation currency points lost per day overdue (R8)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>score_penalty_past_due</t>
+          <t>score_penalty_open_critical</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Issue remediation points lost per finding past due (R8)</t>
+          <t>Issue remediation points lost per open Critical finding (R8)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>score_mrc_conditional</t>
+          <t>score_penalty_open_medium</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1908,132 +1908,132 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MRC compliance score for a Conditional decision with open conditions (R8)</t>
+          <t>Issue remediation points lost per open Medium finding (R8)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>import_max_file_mb</t>
+          <t>score_penalty_open_low</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Governance score</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Maximum size of one structured import file (Excel/CSV)</t>
+          <t>Issue remediation points lost per open Low finding (R8)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>import_max_files</t>
+          <t>score_penalty_past_due</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Governance score</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Maximum number of files in one import batch</t>
+          <t>Issue remediation points lost per finding past due (R8)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>import_max_rows</t>
+          <t>score_mrc_conditional</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Governance score</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Maximum data rows in one import file</t>
+          <t>MRC compliance score for a Conditional decision with open conditions (R8)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>document_type_keywords</t>
+          <t>import_max_file_mb</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Terms of Reference=terms of reference|tor; Model Development Document=model development|mdd|development document; Validation Report=validation report|validation|vr; Monitoring Plan=monitoring plan|mon plan; Backtesting Report=backtesting|backtest; Monitoring Report=monitoring report|monitoring|kpi; Model Approval/MRC Paper=mrc|approval|committee paper; Model Change Document=model change|change request; Data Quality Report=data quality|dq report|dq; Regulatory/Audit Evidence=regulatory|audit|supervisory; Model Inventory Evidence=inventory</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Classification keywords per document type, checked in this order against file then folder names (BRD §34)</t>
+          <t>Maximum size of one structured import file (Excel/CSV)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>allowed_document_extensions</t>
+          <t>import_max_files</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>pdf; docx; xlsx; pptx; csv</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2043,51 +2043,51 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>File types accepted as documents or evidence</t>
+          <t>Maximum number of files in one import batch</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>document_confidentiality_levels</t>
+          <t>import_max_rows</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Internal; Confidential; Restricted</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Confidentiality classifications</t>
+          <t>Maximum data rows in one import file</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>document_default_confidentiality</t>
+          <t>document_type_keywords</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Terms of Reference=terms of reference|tor; Model Development Document=model development|mdd|development document; Validation Report=validation report|validation|vr; Monitoring Plan=monitoring plan|mon plan; Backtesting Report=backtesting|backtest; Monitoring Report=monitoring report|monitoring|kpi; Model Approval/MRC Paper=mrc|approval|committee paper; Model Change Document=model change|change request; Data Quality Report=data quality|dq report|dq; Regulatory/Audit Evidence=regulatory|audit|supervisory; Model Inventory Evidence=inventory</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2097,51 +2097,51 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Confidentiality applied when none is given</t>
+          <t>Classification keywords per document type, checked in this order against file then folder names (BRD §34)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>document_retention_years</t>
+          <t>allowed_document_extensions</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>pdf; docx; xlsx; pptx; csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Files</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Retention period from the effective date (BRD §68)</t>
+          <t>File types accepted as documents or evidence</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>document_auto_confirm_confidence</t>
+          <t>document_confidentiality_levels</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>Internal; Confidential; Restricted</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2151,46 +2151,46 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Minimum classification confidence for a system (seed) load to store without review</t>
+          <t>Confidentiality classifications</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>max_zip_uncompressed_mb</t>
+          <t>document_default_confidentiality</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Maximum total size of files inside a ZIP package</t>
+          <t>Confidentiality applied when none is given</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>max_zip_compression_ratio</t>
+          <t>document_retention_years</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2200,64 +2200,145 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reject ZIP members compressed more than this ratio (zip-bomb guard)</t>
+          <t>Retention period from the effective date (BRD §68)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>production_phases</t>
+          <t>document_auto_confirm_confidence</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Monitoring; Reg/Audit</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lifecycle phases counted as 'in production' on the Command Center</t>
+          <t>Minimum classification confidence for a system (seed) load to store without review</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>max_zip_uncompressed_mb</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Maximum total size of files inside a ZIP package</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>max_zip_compression_ratio</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Reject ZIP members compressed more than this ratio (zip-bomb guard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>production_phases</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Monitoring; Reg/Audit</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Lifecycle phases counted as 'in production' on the Command Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>insights_display_limit</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Number of governance insights shown on the Command Center (all are available on request)</t>
         </is>
